--- a/templates/highschool_input.xlsx
+++ b/templates/highschool_input.xlsx
@@ -21533,7 +21533,7 @@
       <formula2>DATE(2026,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="B2:B3000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="목록에서 고르세요." type="list">
-      <formula1>"주말리그 전반기,주말리그 후반기,황금사자기,청룡기,봉황대기,기타"</formula1>
+      <formula1>"주말리그 전반기,주말리그 후반기,신세계 이마트배,황금사자기,청룡기,대통령배,봉황대기,기타"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C3000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="경기 번호는 1~999 정수 (같은 날 두 경기를 구분)" type="whole" operator="between">
       <formula1>1</formula1>
